--- a/Mantenimiento/excels/LAMBAYEQUE-CHICLAYO-LA_VICTORIA.xlsx
+++ b/Mantenimiento/excels/LAMBAYEQUE-CHICLAYO-LA_VICTORIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -664,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,7 +738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -820,7 +785,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -872,7 +832,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -924,7 +879,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -976,7 +926,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1028,7 +973,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,7 +1020,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1132,7 +1067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA_VICTORIA</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1211,11 +1141,6 @@
       </c>
       <c r="K15" t="n">
         <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LAMBAYEQUE-CHICLAYO-LA_VICTORIA.xlsx
+++ b/Mantenimiento/excels/LAMBAYEQUE-CHICLAYO-LA_VICTORIA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>008 NIÑO MENSAJEROS DE LA PAZ</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.79296</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.84444000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>305</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.79296</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.84444</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>041 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.801928</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.836234</v>
-      </c>
-      <c r="I3" t="n">
-        <v>237</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.801928</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.836234</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>10717 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.79898</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.83665000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2352</v>
-      </c>
-      <c r="J4" t="n">
-        <v>117</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.79898</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.83665</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>10796 CARLOS AUGUSTO SALAVERRY</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.798454</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.847853</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J5" t="n">
-        <v>77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.798454</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.847853</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>11025 JUAN PABLO VIZCARDO Y GUZMAN</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.7955</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.83346</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1497</v>
-      </c>
-      <c r="J6" t="n">
-        <v>64</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.7955</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.83346</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>11026 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.79288</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.84204</v>
-      </c>
-      <c r="I7" t="n">
-        <v>927</v>
-      </c>
-      <c r="J7" t="n">
-        <v>36</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.79288</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.84204</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>11098 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.80328</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.83613</v>
-      </c>
-      <c r="I8" t="n">
-        <v>454</v>
-      </c>
-      <c r="J8" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.80328</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.83613</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>SAGRADO MAESTRO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.7942</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.84381999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>319</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.7942</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.84382</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>EL PEREGRINO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.79989</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.84249</v>
-      </c>
-      <c r="I10" t="n">
-        <v>402</v>
-      </c>
-      <c r="J10" t="n">
-        <v>26</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.79989</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.84249</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>COLEGIO DE INNOVADORES VANGUARDIA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.79548</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.8429</v>
-      </c>
-      <c r="I11" t="n">
-        <v>258</v>
-      </c>
-      <c r="J11" t="n">
-        <v>22</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.79548</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.8429</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>ADEU</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.79242892026726</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.8468957397466</v>
-      </c>
-      <c r="I12" t="n">
-        <v>438</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.79242892026726</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.8468957397466</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>COLEGIOS Y ACADEMIAS MONTESSORI EIR</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.80001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.84468</v>
-      </c>
-      <c r="I13" t="n">
-        <v>177</v>
-      </c>
-      <c r="J13" t="n">
-        <v>13</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.80001</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.84468</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>SANTA ANA SCHOOL</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.79047</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.84162000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>340</v>
-      </c>
-      <c r="J14" t="n">
-        <v>19</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.79047</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.84162</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>NEW PEOPLE KIDS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-6.787949</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.843757</v>
-      </c>
-      <c r="I15" t="n">
-        <v>213</v>
-      </c>
-      <c r="J15" t="n">
-        <v>16</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.787949</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.843757</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
